--- a/BigNumber.xlsx
+++ b/BigNumber.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0facb8bd3b87b23f/Documentos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3760DD1-A8BF-47A4-8A78-BFC5924C46FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{A3760DD1-A8BF-47A4-8A78-BFC5924C46FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A36F1B0A-9E91-4A80-9679-A28276B959C4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C049048A-7FE4-450B-8D36-AFF85BE9D56A}"/>
   </bookViews>
@@ -17,23 +17,39 @@
   </sheets>
   <definedNames>
     <definedName name="BigAbs">_xlfn.LAMBDA(_xlpm.a, ABS( VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) ) &amp; "e"&amp; MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99) )</definedName>
-    <definedName name="BigAdd">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, (VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) + VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1))) &amp;"e"&amp; VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) )</definedName>
+    <definedName name="BigAdd">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( ABS( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) - VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)) )&gt;15,  IF( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) &gt; VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), _xlpm.a, _xlpm.b ),  ( VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) * 10^( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) - MAX( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)), VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)) ) ) + VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)) * 10^( VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)) - MAX( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)), VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)) ) ) ) &amp; "e" &amp; MAX( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)), VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)) ) ) )</definedName>
+    <definedName name="BigAnd">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( AND( BigCompare(_xlpm.a,"0e0")&lt;&gt;0, BigCompare(_xlpm.b,"0e0")&lt;&gt;0 ), 1, 0 ) )</definedName>
+    <definedName name="BigCompare">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( BigGT(_xlpm.a,_xlpm.b), 1, IF( BigLT(_xlpm.a,_xlpm.b), -1, 0 ) ) )</definedName>
     <definedName name="BigConstructor">_xlfn.LAMBDA(_xlpm.m,_xlpm.e,_xlfn.CONCAT(_xlpm.m,"e",_xlpm.e))</definedName>
+    <definedName name="BigCos">_xlfn.LAMBDA(_xlpm.a, COS( BigToNumber(_xlpm.a) ) )</definedName>
     <definedName name="BigDiv">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, (VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) / VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1))) &amp;"e"&amp; (VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) - VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99))) )</definedName>
     <definedName name="BigEQ">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( AND( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))= VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1))= VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)) ), 1, 0 ) )</definedName>
+    <definedName name="BigExponent">_xlfn.LAMBDA(_xlpm.a, MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99) )</definedName>
     <definedName name="BigFormatExp">_xlfn.LAMBDA(_xlpm.exp, IF( LEN(_xlpm.exp)&lt;=10, _xlpm.exp, LEFT(_xlpm.exp,1)&amp;","&amp; MID(_xlpm.exp,2,6)&amp; "e"&amp; (LEN(_xlpm.exp)-1) ) )</definedName>
     <definedName name="BigGT">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))&gt; VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), 1, IF( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))&lt; VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), 0, IF( VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1))&gt; VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)), 1, 0 ) ) ) )</definedName>
     <definedName name="BigGTE">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( OR( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))&gt; VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), AND( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))= VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1))&gt;= VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)) ) ), 1, 0 ) )</definedName>
     <definedName name="BigIF">_xlfn.LAMBDA(_xlpm.cond,_xlpm.valorSiVerdadero,_xlpm.valorSiFalso, IF(_xlpm.cond=1, _xlpm.valorSiVerdadero, _xlpm.valorSiFalso ) )</definedName>
+    <definedName name="BigIsNegative">_xlfn.LAMBDA(_xlpm.a, IF( BigCompare(_xlpm.a,"0e0")=-1, 1, 0 ) )+Hoja1!$I$18</definedName>
+    <definedName name="BigIsPositive">_xlfn.LAMBDA(_xlpm.a, IF( BigCompare(_xlpm.a,"0e0")=1, 1, 0 ) )+Hoja1!$I$19</definedName>
+    <definedName name="BigIsZero">_xlfn.LAMBDA(_xlpm.a, IF( BigCompare(_xlpm.a,"0e0")=0, 1, 0 ) )</definedName>
     <definedName name="BigLOG10">_xlfn.LAMBDA(_xlpm.a,LOG10( VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) ) + VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) )</definedName>
+    <definedName name="BigLogBASE">_xlfn.LAMBDA(_xlpm.a,_xlpm.base, (LOG10( VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) ) + VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) ) /LOG10(_xlpm.base) )</definedName>
     <definedName name="BigLT">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(BigGT(_xlpm.a,_xlpm.b)=1,0, IF( AND( VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99))= VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99)), VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1))= VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)) ), 0, 1 ) ) )</definedName>
     <definedName name="BigLTE">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(BigGT(_xlpm.a,_xlpm.b)=1,0,1) )</definedName>
+    <definedName name="BigMantissa">_xlfn.LAMBDA(_xlpm.a, VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) )</definedName>
     <definedName name="BigMul">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, (VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) * VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1))) &amp;"e"&amp; (VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) + VALUE(MID(_xlpm.b,SEARCH("e",_xlpm.b)+1,99))) )</definedName>
     <definedName name="BigNeg">_xlfn.LAMBDA(_xlpm.a, (-VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1))) &amp; "e"&amp; MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99) )</definedName>
     <definedName name="BigNEQ">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF(_xlpm.a&lt;&gt;_xlpm.b,1,0) )</definedName>
     <definedName name="BigNorm">_xlfn.LAMBDA(_xlpm.x, _xlfn.LET( _xlpm.m,VALUE(LEFT(_xlpm.x,SEARCH("e",_xlpm.x)-1)), _xlpm.e,VALUE(MID(_xlpm.x,SEARCH("e",_xlpm.x)+1,99)),  _xlpm.factor,INT(LOG10(ABS(_xlpm.m))),  IF(_xlpm.m=0, "0e0", IF(ABS(_xlpm.m)&gt;=10, (_xlpm.m/10^_xlpm.factor)&amp;"e"&amp;(_xlpm.e+_xlpm.factor), IF(ABS(_xlpm.m)&lt;1, (_xlpm.m*10^ABS(_xlpm.factor))&amp;"e"&amp;(_xlpm.e-ABS(_xlpm.factor)), _xlpm.x ) ) ) ) )</definedName>
+    <definedName name="BigNOT">_xlfn.LAMBDA(_xlpm.a, IF( BigCompare(_xlpm.a,"0e0")&lt;&gt;0, 0, 1 ) )</definedName>
+    <definedName name="BigOr">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( OR( BigCompare(_xlpm.a,"0e0")&lt;&gt;0, BigCompare(_xlpm.b,"0e0")&lt;&gt;0 ), 1, 0 ) )</definedName>
     <definedName name="BigPower">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, "1e"&amp; BigFormatExp( TEXT( INT( VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1)) * BigLOG10(_xlpm.a) ), "0" ) ) )</definedName>
+    <definedName name="BigRound">_xlfn.LAMBDA(_xlpm.a,_xlpm.d, ROUND( BigMantissa(_xlpm.a), _xlpm.d ) &amp; "e" &amp; BigExponent(_xlpm.a) )</definedName>
+    <definedName name="BigSin">_xlfn.LAMBDA(_xlpm.a, SIN( BigToNumber(_xlpm.a) ) )</definedName>
     <definedName name="BigSub">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, (VALUE(LEFT(_xlpm.a,SEARCH("e",_xlpm.a)-1)) - VALUE(LEFT(_xlpm.b,SEARCH("e",_xlpm.b)-1))) &amp;"e"&amp; VALUE(MID(_xlpm.a,SEARCH("e",_xlpm.a)+1,99)) )</definedName>
+    <definedName name="BigTan">_xlfn.LAMBDA(_xlpm.a, TAN( BigToNumber(_xlpm.a) ) )</definedName>
+    <definedName name="BigToNumber">_xlfn.LAMBDA(_xlpm.a, BigMantissa(_xlpm.a) * 10^BigExponent(_xlpm.a) )</definedName>
+    <definedName name="BigXor">_xlfn.LAMBDA(_xlpm.a,_xlpm.b, IF( ( (BigCompare(_xlpm.a,"0e0")&lt;&gt;0) + (BigCompare(_xlpm.b,"0e0")&lt;&gt;0) )=1, 1, 0 ) )</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -131,10 +147,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -458,9 +470,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="str" cm="1">
-        <f t="array" ref="A1">BigAbs("-5e100")</f>
-        <v>5e100</v>
+      <c r="A1" s="1" cm="1">
+        <f t="array" ref="A1">BigLogBASE("1e1000",12)</f>
+        <v>926.62840802912672</v>
       </c>
       <c r="H1"/>
     </row>
